--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.33034187811938</v>
+        <v>11.4286805551944</v>
       </c>
       <c r="D2" t="n">
-        <v>33.12902261730029</v>
+        <v>5.383466175311298</v>
       </c>
       <c r="E2" t="n">
-        <v>3.932224930580048</v>
+        <v>0.6389865512192578</v>
       </c>
       <c r="F2" t="n">
-        <v>12.38992079982891</v>
+        <v>2.013362129972198</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.46589201695929</v>
+        <v>10.15070745275588</v>
       </c>
       <c r="D3" t="n">
-        <v>57.90886421695812</v>
+        <v>9.410190435255695</v>
       </c>
       <c r="E3" t="n">
-        <v>3.932224930580048</v>
+        <v>0.6389865512192578</v>
       </c>
       <c r="F3" t="n">
-        <v>12.38992079982891</v>
+        <v>2.013362129972198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
